--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T17:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:40+00:00</t>
+    <t>2023-05-05T20:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:44:23+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-09T07:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:35:55+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -260,7 +260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -349,37 +349,45 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>27</v>
       </c>
     </row>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-pregnant</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-patient-pregnant</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-patient-pregnant</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-pregnant</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-pregnant</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-patient-pregnant</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-patient-pregnant</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-pregnant</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:13:26+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-patient-pregnant.xlsx
+++ b/ValueSet-vs-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:20:07+00:00</t>
+    <t>2023-07-05T16:42:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -248,10 +248,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
